--- a/Documents/メニュー画面設計書.xlsx
+++ b/Documents/メニュー画面設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CB5485-D96F-469D-B76B-19BC0266ADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C95428C-6EB8-4B00-A9E2-80C16DCE9DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
   </bookViews>
@@ -1208,15 +1208,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1231,7 +1231,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="142875" y="1752600"/>
+          <a:off x="133350" y="2085975"/>
           <a:ext cx="1200150" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1281,15 +1281,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1304,7 +1304,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="142875" y="2219325"/>
+          <a:off x="123825" y="2514600"/>
           <a:ext cx="1200150" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1354,15 +1354,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1377,8 +1377,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="161925" y="2647950"/>
-          <a:ext cx="1219200" cy="285750"/>
+          <a:off x="123825" y="2924175"/>
+          <a:ext cx="1190625" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1422,6 +1422,125 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>361951</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="テキスト ボックス 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F248AD3-ABCE-1DED-0913-ACBB4DB8858B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="57151" y="1485900"/>
+          <a:ext cx="1333500" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>メニュー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1085850</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8693DC4-EEFE-CA21-8860-288D9B7B137C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9525" y="1924050"/>
+          <a:ext cx="8791575" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3017,7 +3136,7 @@
       </c>
       <c r="G2" s="58"/>
       <c r="H2" s="59">
-        <v>45806</v>
+        <v>45810</v>
       </c>
       <c r="I2" s="60"/>
       <c r="J2" s="61"/>

--- a/Documents/メニュー画面設計書.xlsx
+++ b/Documents/メニュー画面設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB4033B-C0F6-4255-821B-9F92A46A20BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E141A5-C23E-4CAF-B279-02C7D534BA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
   </bookViews>
@@ -711,6 +711,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -738,9 +759,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -785,24 +803,6 @@
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1113,13 +1113,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1085850</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1134,7 +1134,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="9525" y="1924050"/>
+          <a:off x="9525" y="2000250"/>
           <a:ext cx="8791575" cy="19050"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1349,6 +1349,142 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE449C19-B7F0-B7D3-3960-18AC32A53DC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7258050" y="1543050"/>
+          <a:ext cx="1771650" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ユーザー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>：〇〇〇</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト ボックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56DC602E-DC8F-4026-A6C9-C83B06660BD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7248525" y="1724025"/>
+          <a:ext cx="1771650" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ユーザー名：〇〇〇</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1668,19 +1804,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="36" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="36" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="22"/>
+      <c r="G1" s="29"/>
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1692,67 +1828,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="37" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="37" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="38"/>
-      <c r="H2" s="40">
+      <c r="G2" s="44"/>
+      <c r="H2" s="46">
         <v>45810</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="18"/>
+      <c r="J2" s="25"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="19"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="19"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="24"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="12"/>
@@ -1766,91 +1902,91 @@
       <c r="J6" s="15"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="29"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="31"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="29"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="37"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="12"/>
@@ -1864,7 +2000,7 @@
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="12"/>
@@ -1882,7 +2018,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="12"/>
@@ -1899,7 +2035,7 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="H16" s="22" t="s">
         <v>0</v>
       </c>
       <c r="I16" s="12"/>
@@ -2008,16 +2144,16 @@
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="46"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -2998,6 +3134,27 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A23:C23"/>
@@ -3008,27 +3165,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/メニュー画面設計書.xlsx
+++ b/Documents/メニュー画面設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E141A5-C23E-4CAF-B279-02C7D534BA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BCF2F3-DB7F-4F0C-9496-052C373F152D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
   </bookViews>
@@ -140,22 +140,22 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>form="logout.jsp"へ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>form="task-add-form.jsp"へ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>form=".jsp"へ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>山形</t>
     <rPh sb="0" eb="2">
       <t>ヤマガタ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>form action=".jsp"へ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>form action="task-add-form.jsp"へ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>form action="logout.jsp"へ</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -696,21 +696,99 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -725,84 +803,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1804,19 +1804,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="29"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1828,67 +1828,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="46">
+      <c r="G2" s="28"/>
+      <c r="H2" s="30">
         <v>45810</v>
       </c>
-      <c r="I2" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="25"/>
+      <c r="I2" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="33"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="26"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="31"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="38"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="12"/>
@@ -1899,94 +1899,94 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="15"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="34"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="17"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="37"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="12"/>
@@ -1997,19 +1997,19 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="15"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="39"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5" t="s">
         <v>13</v>
       </c>
@@ -2018,11 +2018,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -2035,18 +2035,18 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="40" t="s">
         <v>0</v>
       </c>
       <c r="I16" s="12"/>
-      <c r="J16" s="15"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="11">
+      <c r="A17" s="41">
         <v>1</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="7" t="s">
         <v>24</v>
       </c>
@@ -2057,18 +2057,18 @@
       <c r="G17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="14" t="s">
-        <v>30</v>
+      <c r="H17" s="39" t="s">
+        <v>29</v>
       </c>
       <c r="I17" s="12"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="11">
+      <c r="A18" s="41">
         <v>2</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
         <v>25</v>
       </c>
@@ -2079,18 +2079,18 @@
       <c r="G18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="14" t="s">
-        <v>29</v>
+      <c r="H18" s="39" t="s">
+        <v>30</v>
       </c>
       <c r="I18" s="12"/>
-      <c r="J18" s="15"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="11">
+      <c r="A19" s="41">
         <v>3</v>
       </c>
       <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
@@ -2101,59 +2101,59 @@
       <c r="G19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="14" t="s">
-        <v>28</v>
+      <c r="H19" s="39" t="s">
+        <v>31</v>
       </c>
       <c r="I19" s="12"/>
-      <c r="J19" s="15"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="11"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="14"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="12"/>
-      <c r="J20" s="15"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="11"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="14"/>
+      <c r="H21" s="39"/>
       <c r="I21" s="12"/>
-      <c r="J21" s="15"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="11"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="14"/>
+      <c r="H22" s="39"/>
       <c r="I22" s="12"/>
-      <c r="J22" s="15"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="20"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3134,6 +3134,22 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -3149,22 +3165,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/メニュー画面設計書.xlsx
+++ b/Documents/メニュー画面設計書.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BCF2F3-DB7F-4F0C-9496-052C373F152D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F39129-02C1-4ADE-8F1D-F10628AAFA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
   </bookViews>
   <sheets>
     <sheet name="画面設計書" sheetId="3" r:id="rId1"/>
+    <sheet name="画面遷移図" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>備考</t>
   </si>
@@ -158,6 +159,20 @@
     <t>form action="logout.jsp"へ</t>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>画面遷移図</t>
+  </si>
+  <si>
+    <t>taskUN</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>56期</t>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
@@ -229,7 +244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -654,6 +669,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -662,7 +756,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -696,17 +790,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -780,28 +898,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1494,6 +1624,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3444B84-1D2B-B096-8153-8413CE78D339}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="257175" y="1038225"/>
+          <a:ext cx="7772400" cy="4295775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -1804,19 +1989,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1828,67 +2013,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="27" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="27" t="s">
+      <c r="E2" s="36"/>
+      <c r="F2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="30">
+      <c r="G2" s="36"/>
+      <c r="H2" s="38">
         <v>45810</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="33"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="34"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="34"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="37" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="38"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="12"/>
@@ -1899,94 +2084,94 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="17"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="25"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="20"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="20"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="20"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="20"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="12"/>
@@ -1997,19 +2182,19 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="13"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="39"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
-      <c r="H15" s="14"/>
+      <c r="H15" s="13"/>
       <c r="I15" s="5" t="s">
         <v>13</v>
       </c>
@@ -2018,11 +2203,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="14"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -2035,18 +2220,18 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="22" t="s">
         <v>0</v>
       </c>
       <c r="I16" s="12"/>
-      <c r="J16" s="13"/>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41">
+      <c r="A17" s="11">
         <v>1</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="14"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="7" t="s">
         <v>24</v>
       </c>
@@ -2057,18 +2242,18 @@
       <c r="G17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I17" s="12"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41">
+      <c r="A18" s="11">
         <v>2</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="14"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="7" t="s">
         <v>25</v>
       </c>
@@ -2079,18 +2264,18 @@
       <c r="G18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="12"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41">
+      <c r="A19" s="11">
         <v>3</v>
       </c>
       <c r="B19" s="12"/>
-      <c r="C19" s="14"/>
+      <c r="C19" s="13"/>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
@@ -2101,59 +2286,59 @@
       <c r="G19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="12"/>
-      <c r="C20" s="14"/>
+      <c r="C20" s="13"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="39"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="12"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
+      <c r="A21" s="11"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="14"/>
+      <c r="C21" s="13"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="39"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
+      <c r="A22" s="11"/>
       <c r="B22" s="12"/>
-      <c r="C22" s="14"/>
+      <c r="C22" s="13"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="39"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="12"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="46"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3134,22 +3319,6 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -3165,10 +3334,1449 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641D4BF-09B1-476C-ACD4-D079D3240563}">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="4.5" style="4" customWidth="1"/>
+    <col min="4" max="10" width="14.625" style="4" customWidth="1"/>
+    <col min="11" max="26" width="7.625" style="4" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="34"/>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="36"/>
+      <c r="F2" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="36"/>
+      <c r="H2" s="38">
+        <v>45818</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="55"/>
+    </row>
+    <row r="6" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
+    </row>
+    <row r="7" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55"/>
+    </row>
+    <row r="9" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="55"/>
+    </row>
+    <row r="11" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="55"/>
+    </row>
+    <row r="13" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+    </row>
+    <row r="15" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="55"/>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="55"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="55"/>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A20" s="53"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="55"/>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A21" s="53"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="55"/>
+    </row>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A22" s="53"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+    </row>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A23" s="53"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="55"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A24" s="53"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="55"/>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A25" s="53"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A26" s="53"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="55"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A27" s="53"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="55"/>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="55"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="55"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="55"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A31" s="53"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="55"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="55"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="55"/>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A34" s="56"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="58"/>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Documents/メニュー画面設計書.xlsx
+++ b/Documents/メニュー画面設計書.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F39129-02C1-4ADE-8F1D-F10628AAFA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE4C3A9-3A51-4AAE-805B-C74455B36511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BF67F2DF-57B3-4641-80B4-FE0311ACF769}"/>
   </bookViews>
   <sheets>
-    <sheet name="画面設計書" sheetId="3" r:id="rId1"/>
-    <sheet name="画面遷移図" sheetId="4" r:id="rId2"/>
+    <sheet name="表紙" sheetId="5" r:id="rId1"/>
+    <sheet name="画面設計書" sheetId="3" r:id="rId2"/>
+    <sheet name="画面遷移図" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>備考</t>
   </si>
@@ -173,12 +174,38 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>プロジェクト型演習　成果ドキュメント</t>
+  </si>
+  <si>
+    <t>初版</t>
+  </si>
+  <si>
+    <t>YYYY/MM/DD</t>
+  </si>
+  <si>
+    <t>メニュー画面機能</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>山形みづき</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマガタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +256,36 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -244,7 +301,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -748,6 +805,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -756,7 +822,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -790,21 +856,117 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -820,82 +982,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -910,29 +1000,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1975,6 +2068,1177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA072FB-6AAB-443E-8EFC-7095CEA3646F}">
+  <dimension ref="C1:P1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16" width="6.75" style="4" customWidth="1"/>
+    <col min="17" max="26" width="7.625" style="4" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
+    <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
+      <c r="C2" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61"/>
+    </row>
+    <row r="3" spans="3:16" ht="30" customHeight="1">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="61"/>
+    </row>
+    <row r="4" spans="3:16" ht="30" customHeight="1">
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="61"/>
+    </row>
+    <row r="5" spans="3:16" ht="30" customHeight="1">
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="61"/>
+    </row>
+    <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="61"/>
+    </row>
+    <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="61"/>
+    </row>
+    <row r="8" spans="3:16" ht="30" customHeight="1">
+      <c r="E8" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+    </row>
+    <row r="9" spans="3:16" ht="30" customHeight="1"/>
+    <row r="10" spans="3:16" ht="30" customHeight="1"/>
+    <row r="11" spans="3:16" ht="30" customHeight="1"/>
+    <row r="12" spans="3:16" ht="30" customHeight="1"/>
+    <row r="13" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G13" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G14" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="67">
+        <v>45828</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G15" s="64"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+    </row>
+    <row r="17" spans="7:11" ht="30" customHeight="1">
+      <c r="G17" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
+    <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
+    <row r="20" spans="7:11" ht="24.75" customHeight="1"/>
+    <row r="21" spans="7:11" ht="24.75" customHeight="1"/>
+    <row r="22" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="23" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="24" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="25" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="26" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="27" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="28" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="29" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="30" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="31" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="32" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="C2:O6"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A755C6C-49D6-47A2-B0D3-A1E867EBDD24}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1989,19 +3253,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="33" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="34"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
@@ -2013,188 +3277,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="35" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="35" t="s">
+      <c r="E2" s="34"/>
+      <c r="F2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="38">
+      <c r="G2" s="34"/>
+      <c r="H2" s="36">
         <v>45810</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="41"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="42"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="42"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="45" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="15"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="23"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="28"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="28"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="26"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="26"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="28"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="15"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="5" t="s">
         <v>13</v>
       </c>
@@ -2203,11 +3467,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -2220,18 +3484,18 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="15"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="11">
+      <c r="A17" s="47">
         <v>1</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="7" t="s">
         <v>24</v>
       </c>
@@ -2242,18 +3506,18 @@
       <c r="G17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="15"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="11">
+      <c r="A18" s="47">
         <v>2</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="7" t="s">
         <v>25</v>
       </c>
@@ -2264,18 +3528,18 @@
       <c r="G18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="15"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="11">
+      <c r="A19" s="47">
         <v>3</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
@@ -2286,59 +3550,59 @@
       <c r="G19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="15"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="15"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="15"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="15"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="20"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3319,6 +4583,22 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -3334,22 +4614,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -3358,7 +4622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641D4BF-09B1-476C-ACD4-D079D3240563}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
@@ -3370,19 +4634,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="33" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="34"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
@@ -3394,408 +4658,408 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="35" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="35" t="s">
+      <c r="E2" s="34"/>
+      <c r="F2" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="38">
+      <c r="G2" s="34"/>
+      <c r="H2" s="36">
         <v>45818</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="41"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="42"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="47"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="52"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="53"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="55"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="53"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="55"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="55"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="55"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="55"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="55"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="55"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="55"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="55"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="55"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="55"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="55"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="55"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="55"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="55"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="53"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="55"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="53"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="55"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="55"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="53"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="55"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="55"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="55"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="55"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="55"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="55"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="53"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="55"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="13"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="53"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="55"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="53"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="55"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="13"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="53"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="55"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A34" s="56"/>
-      <c r="B34" s="57"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="58"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
